--- a/sources/jin_step5.xlsx
+++ b/sources/jin_step5.xlsx
@@ -417,27 +417,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R138"/>
+  <dimension ref="A1:S138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="31" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
     <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="157" customWidth="1" min="14" max="14"/>
-    <col width="38" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="157" customWidth="1" min="15" max="15"/>
     <col width="38" customWidth="1" min="16" max="16"/>
     <col width="38" customWidth="1" min="17" max="17"/>
-    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="38" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -465,12 +466,12 @@
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="F2" s="1" t="inlineStr">
@@ -495,45 +496,50 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
+          <t>Damage Sum</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
+      <c r="L2" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="L2" s="1" t="inlineStr">
+      <c r="M2" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="M2" s="1" t="inlineStr">
+      <c r="N2" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="N2" s="1" t="inlineStr">
+      <c r="O2" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="O2" s="1" t="inlineStr">
+      <c r="P2" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="P2" s="1" t="inlineStr">
+      <c r="Q2" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Q2" s="1" t="inlineStr">
+      <c r="R2" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="R2" s="1" t="inlineStr">
+      <c r="S2" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -560,22 +566,27 @@
           <t>10,20</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>1fc23c0d-27d6-4421-ae04-82e296cfe349</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>846c1d82-acd7-471d-a898-6519f622274a</t>
         </is>
@@ -602,22 +613,27 @@
           <t>30</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>0376c747-3555-4bcd-a34b-40834f2b731b</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>1bba05e3-1125-4b29-9190-3335d5e3e198</t>
         </is>
@@ -644,27 +660,32 @@
           <t>33</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>1+2</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Opponent can tech roll after the throw.; Special Tag Throw with Jun only. Jun finishes with a Reverse Arm Bar. Total damage is 30.</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>6c991783-0346-4871-bf41-7746cc045080</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>13d40c7e-6854-454c-8bf9-a45114c252dc</t>
         </is>
@@ -691,22 +712,27 @@
           <t>35</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>7163c970-ac14-4802-bd65-2eede14a895e</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>81ac5bc6-daac-4ef9-9c20-a996a21953e5</t>
         </is>
@@ -733,22 +759,27 @@
           <t>35</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>979632c7-e5b6-48a3-be68-3f5d10e4cda3</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>ec1af669-5e82-4d16-ab19-60f60b48d325</t>
         </is>
@@ -757,7 +788,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FC 1+2</t>
+          <t>FC+1+2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -775,22 +806,27 @@
           <t>5</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>System</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>8a32a40c-eb99-4c3e-83d9-8fb9cb6f62c4</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -812,22 +848,27 @@
           <t>5,5,5,5,5</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t>System</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>9b654aae-43b4-4ee3-835c-083e97efa144</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>8a32a40c-eb99-4c3e-83d9-8fb9cb6f62c4</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -849,22 +890,27 @@
           <t>5,5,5,5,5</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t>System</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>7cbf5cdd-f696-407b-bc8d-f553aec297ca</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>8a32a40c-eb99-4c3e-83d9-8fb9cb6f62c4</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -886,22 +932,27 @@
           <t>5,5,5,25</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
         <is>
           <t>System</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>9c909692-e175-413c-bb3d-d48e4dbe578e</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>8a32a40c-eb99-4c3e-83d9-8fb9cb6f62c4</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -923,22 +974,27 @@
           <t>5,5,5,25</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>System</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>767ed810-48c3-4120-acc7-99c5a2660fcb</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>8a32a40c-eb99-4c3e-83d9-8fb9cb6f62c4</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -960,22 +1016,27 @@
           <t>25</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t>System</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>cda82971-a307-467e-ad05-57768181324c</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>8a32a40c-eb99-4c3e-83d9-8fb9cb6f62c4</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1002,22 +1063,27 @@
           <t>12,19</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t>Left</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>823249d7-37de-46b1-879b-61503eaa94c3</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1044,22 +1110,27 @@
           <t>40</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t>Right</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>25dd8959-e3d5-46b4-9df3-7e812375a7d4</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1086,22 +1157,27 @@
           <t>60</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>Back</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>67cda8df-b3c2-4b5d-83b0-595685761a80</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1133,12 +1209,12 @@
       </c>
       <c r="D19" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="E19" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="F19" s="1" t="inlineStr">
@@ -1163,45 +1239,50 @@
       </c>
       <c r="J19" s="1" t="inlineStr">
         <is>
+          <t>Damage Sum</t>
+        </is>
+      </c>
+      <c r="K19" s="1" t="inlineStr">
+        <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="K19" s="1" t="inlineStr">
+      <c r="L19" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="L19" s="1" t="inlineStr">
+      <c r="M19" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="M19" s="1" t="inlineStr">
+      <c r="N19" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="N19" s="1" t="inlineStr">
+      <c r="O19" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="O19" s="1" t="inlineStr">
+      <c r="P19" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="P19" s="1" t="inlineStr">
+      <c r="Q19" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Q19" s="1" t="inlineStr">
+      <c r="R19" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="R19" s="1" t="inlineStr">
+      <c r="S19" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -1240,15 +1321,20 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
           <t>h</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>342c72d2-bcf6-41ff-93b3-455cba39507d</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>85ef1f81-b5b3-415e-9bae-fcad79bbba56</t>
         </is>
@@ -1287,15 +1373,20 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
           <t>h</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>eee61db1-ffb0-42cd-9d84-01ffa73217e7</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>a81778f7-ae79-41ab-937d-b95437a297ee</t>
         </is>
@@ -1304,7 +1395,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>F,1</t>
+          <t>f+1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1334,15 +1425,20 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t>h</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>107f9188-73d0-4ab3-a46c-c694465fc4cf</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>9fa3928f-0448-4225-b081-6487d519a269</t>
         </is>
@@ -1351,7 +1447,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>F,3</t>
+          <t>f+3</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1381,15 +1477,20 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
           <t>h</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>8310c13f-2a53-439d-84a6-e21d2adbfe3d</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>c0642b21-4f24-47e8-8de1-798b9b20189f</t>
         </is>
@@ -1428,15 +1529,20 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
           <t>s</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>952aeaec-c71e-490e-ac17-2449ef159c81</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>a5461e92-5b34-418d-b398-b0ac4a30f19e</t>
         </is>
@@ -1475,15 +1581,20 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
           <t>l</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>2c380826-9f48-4ce3-9225-1a6e5777b005</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>b293d99a-188d-4448-b593-b10a475b3bd5</t>
         </is>
@@ -1492,7 +1603,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>FC 1</t>
+          <t>FC+1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1522,15 +1633,20 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
           <t>s</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>bcc8a48a-d690-483a-9dc9-6a3295d64398</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>571826af-3182-403f-989f-d9e5273324ad</t>
         </is>
@@ -1539,7 +1655,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FC 3</t>
+          <t>FC+3</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1569,15 +1685,20 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
           <t>l</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>638cfdf7-83a7-4a97-b6e5-bbeaa8743669</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>964a3fcd-2c30-4c0f-8014-08b4010f7e0d</t>
         </is>
@@ -1586,7 +1707,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>WS 1</t>
+          <t>WS+1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1616,15 +1737,20 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>6b5b01ce-c27c-4cd0-87d9-0949033451c3</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>98fb20b7-b139-4845-b6e4-055dd57fbc55</t>
         </is>
@@ -1633,7 +1759,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>WS 3</t>
+          <t>WS+3</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1663,15 +1789,20 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t>h</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>f2d3fc36-2331-4f8f-8003-29e811f05736</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>a262030f-def1-42cb-9355-385cc8ada115</t>
         </is>
@@ -1710,15 +1841,20 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>7715ee82-1244-4873-bac1-be236455f34c</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>c2c87c8c-b859-490e-a4db-481ba37cac07</t>
         </is>
@@ -1757,15 +1893,20 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>77a42648-ab94-40c2-b72f-0be90d3cc446</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>b96b2e61-3a45-418c-a2d0-53160a54e19f</t>
         </is>
@@ -1804,15 +1945,20 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
           <t>h</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>8fb641c2-77cf-4f70-ad6d-7fa410ff43b4</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>8618a665-283b-4c18-8ed4-3bdedb71f083</t>
         </is>
@@ -1851,15 +1997,20 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
           <t>h</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>bbe99fd2-88df-4114-9b23-cbbe06d553f8</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>8f89af65-9f24-4425-8445-77193a60c4d0</t>
         </is>
@@ -1868,7 +2019,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>F,2</t>
+          <t>f+2</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1898,15 +2049,20 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>216a966a-76ec-48dc-990d-386d3ec44b3e</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>a01b0e46-5cfb-421e-88d5-f5adb7e35526</t>
         </is>
@@ -1915,7 +2071,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>F,4</t>
+          <t>f+4</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1945,15 +2101,20 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>c43ca22b-0d20-4266-88fa-8466cce93741</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>73458e24-3b00-40b4-bc98-17db997a5de3</t>
         </is>
@@ -1992,15 +2153,20 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
           <t>s</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>af9a36ed-316f-4af4-b580-062e95df18d6</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="Q36" t="inlineStr">
         <is>
           <t>d358bd95-8176-4422-b682-f6e544cdb770</t>
         </is>
@@ -2039,15 +2205,20 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t>l</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>9f0a38ad-35a7-44e8-92c6-dfde6c985ace</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="Q37" t="inlineStr">
         <is>
           <t>6ee036da-686e-48c4-a8b3-f575c520b7c1</t>
         </is>
@@ -2056,7 +2227,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>FC 2</t>
+          <t>FC+2</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2086,15 +2257,20 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
           <t>s</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>21b8abac-673d-4f63-8ea4-76f30d8f2458</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
+      <c r="Q38" t="inlineStr">
         <is>
           <t>0484ffb8-6170-40e5-862e-b2e4a75e5088</t>
         </is>
@@ -2103,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>FC 4</t>
+          <t>FC+4</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2133,15 +2309,20 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
           <t>l</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>494d0c6e-f3cb-4e15-bb22-bfbe22178fb0</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="Q39" t="inlineStr">
         <is>
           <t>32ecf904-b136-4b13-9c64-272262e5cb6c</t>
         </is>
@@ -2150,7 +2331,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>WS 2</t>
+          <t>WS+2</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2180,15 +2361,20 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>f44f31d9-2243-4cb0-b026-0bf6e54e6ce2</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="Q40" t="inlineStr">
         <is>
           <t>1a50f116-8558-47a7-9406-05b4c32218d3</t>
         </is>
@@ -2197,7 +2383,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>WS 4</t>
+          <t>WS+4</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2227,15 +2413,20 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>3df93711-843f-4b92-8603-2cd74965293d</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="Q41" t="inlineStr">
         <is>
           <t>30095be2-2b8b-40d6-a034-79e0f76cf0fb</t>
         </is>
@@ -2274,15 +2465,20 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>74298efc-8cd2-40b0-851c-907bc5877cb3</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="Q42" t="inlineStr">
         <is>
           <t>ba54a51f-ff90-4a01-82c7-8b04eb6672cb</t>
         </is>
@@ -2321,15 +2517,20 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>75e62c9c-68ed-48aa-992b-33fff2dc82d2</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="Q43" t="inlineStr">
         <is>
           <t>7ae6d243-acde-4c58-94fe-0eb235d2833d</t>
         </is>
@@ -2361,12 +2562,12 @@
       </c>
       <c r="D46" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="E46" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="F46" s="1" t="inlineStr">
@@ -2391,45 +2592,50 @@
       </c>
       <c r="J46" s="1" t="inlineStr">
         <is>
+          <t>Damage Sum</t>
+        </is>
+      </c>
+      <c r="K46" s="1" t="inlineStr">
+        <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="K46" s="1" t="inlineStr">
+      <c r="L46" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="L46" s="1" t="inlineStr">
+      <c r="M46" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="M46" s="1" t="inlineStr">
+      <c r="N46" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="N46" s="1" t="inlineStr">
+      <c r="O46" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="O46" s="1" t="inlineStr">
+      <c r="P46" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="P46" s="1" t="inlineStr">
+      <c r="Q46" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Q46" s="1" t="inlineStr">
+      <c r="R46" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="R46" s="1" t="inlineStr">
+      <c r="S46" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -2473,15 +2679,20 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t>hh</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>669cb388-350d-4427-ac35-af60f0c29c11</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="Q47" t="inlineStr">
         <is>
           <t>045eead8-67d6-43d4-b853-5e5cadabd6d4</t>
         </is>
@@ -2520,20 +2731,25 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>a69b1dd2-d4ba-4f1c-b392-c1ae5b5b81c2</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
+      <c r="Q48" t="inlineStr">
         <is>
           <t>0dad6580-c18b-4b95-9d2c-2d0149424352</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr">
+      <c r="R48" t="inlineStr">
         <is>
           <t>669cb388-350d-4427-ac35-af60f0c29c11</t>
         </is>
@@ -2572,25 +2788,30 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
           <t>shh</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>The White Heron cancels the Knee.</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
+      <c r="P49" t="inlineStr">
         <is>
           <t>9688517c-2ed0-4fed-a34d-76e10b004eeb</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
+      <c r="Q49" t="inlineStr">
         <is>
           <t>8c731331-988c-4d9c-8596-7d5f066733b9</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr">
+      <c r="R49" t="inlineStr">
         <is>
           <t>a69b1dd2-d4ba-4f1c-b392-c1ae5b5b81c2</t>
         </is>
@@ -2629,20 +2850,25 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="P50" t="inlineStr">
         <is>
           <t>99016883-22f7-46e2-a6b8-ce5a61a0d420</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
+      <c r="Q50" t="inlineStr">
         <is>
           <t>cf9f2947-d848-4d7e-9c05-30092d50f675</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr">
+      <c r="R50" t="inlineStr">
         <is>
           <t>9688517c-2ed0-4fed-a34d-76e10b004eeb</t>
         </is>
@@ -2681,25 +2907,30 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
           <t>L</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t>JG BS</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="P51" t="inlineStr">
         <is>
           <t>7fc69d38-3ebd-4e97-9de3-fd5c4f4bea32</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="Q51" t="inlineStr">
         <is>
           <t>edf632be-2d1a-4d2c-9c97-04b569692098</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
+      <c r="R51" t="inlineStr">
         <is>
           <t>9688517c-2ed0-4fed-a34d-76e10b004eeb</t>
         </is>
@@ -2743,15 +2974,20 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t>hhm</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
+      <c r="P52" t="inlineStr">
         <is>
           <t>ad864b4e-ead0-4496-91b5-f34a0004c607</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr">
+      <c r="Q52" t="inlineStr">
         <is>
           <t>701beb9c-1194-4ce6-b668-69ef292b6c69</t>
         </is>
@@ -2795,15 +3031,20 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t>hhh</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
+      <c r="P53" t="inlineStr">
         <is>
           <t>a208103e-6af6-44d4-bd61-39c05b0478e5</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr">
+      <c r="Q53" t="inlineStr">
         <is>
           <t>af2f7818-41dc-43c6-8734-be6aec1c5b57</t>
         </is>
@@ -2812,7 +3053,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>WS 1,2 - [~5]</t>
+          <t>WS+1,2 - [~5]</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2847,20 +3088,25 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
+      <c r="P54" t="inlineStr">
         <is>
           <t>92abbd98-841a-40a6-9f2c-f893c21e340e</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr">
+      <c r="Q54" t="inlineStr">
         <is>
           <t>9cbbe317-54bf-4ee0-96d3-1790b5bd954c</t>
         </is>
@@ -2874,7 +3120,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>f+1+2,2; WR 1+2,2</t>
+          <t>f+1+2,2; WR+1+2,2</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2909,20 +3155,25 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t>Damage if the 1st hit is 12 if you don't execute the 2nd hit.</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
+      <c r="P55" t="inlineStr">
         <is>
           <t>55290405-aecb-431d-8776-2711101b6b52</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="Q55" t="inlineStr">
         <is>
           <t>05b3cfcc-36dd-4b14-b695-6372cb45c631</t>
         </is>
@@ -2966,20 +3217,25 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t>On a clean hit damage will be 43 and the opponent is knocked down.</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr">
+      <c r="P56" t="inlineStr">
         <is>
           <t>0319b4a5-9818-44bd-ba56-ebe692edf5e4</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr">
+      <c r="Q56" t="inlineStr">
         <is>
           <t>369503a8-a513-463a-b657-8a6fd30dc8b3</t>
         </is>
@@ -3018,20 +3274,25 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
+      <c r="P57" t="inlineStr">
         <is>
           <t>31143497-6374-4945-ab57-794c3f53f5f0</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr">
+      <c r="Q57" t="inlineStr">
         <is>
           <t>264f8dcc-2d0a-401a-b94f-2acf6b20d9b3</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr">
+      <c r="R57" t="inlineStr">
         <is>
           <t>0319b4a5-9818-44bd-ba56-ebe692edf5e4</t>
         </is>
@@ -3070,25 +3331,30 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
           <t>L</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="N58" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr">
+      <c r="P58" t="inlineStr">
         <is>
           <t>f722eb0e-9ea9-4640-8c8f-071535c4f894</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr">
+      <c r="Q58" t="inlineStr">
         <is>
           <t>2ccd3675-3eda-453b-872c-3ca8e7e7a7cc</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr">
+      <c r="R58" t="inlineStr">
         <is>
           <t>0319b4a5-9818-44bd-ba56-ebe692edf5e4</t>
         </is>
@@ -3132,15 +3398,20 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr">
+      <c r="P59" t="inlineStr">
         <is>
           <t>ae24f3fa-b66c-4c48-af36-424ab0f494d8</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr">
+      <c r="Q59" t="inlineStr">
         <is>
           <t>6357306f-64d7-44d5-b5e5-33a2957ce50a</t>
         </is>
@@ -3184,20 +3455,25 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="N60" t="inlineStr">
         <is>
           <t>MS</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr">
+      <c r="P60" t="inlineStr">
         <is>
           <t>1b2534aa-8b82-4a86-ab3f-f25c4c4483a3</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr">
+      <c r="Q60" t="inlineStr">
         <is>
           <t>b343de68-5a6c-42ae-adc2-f3dc237905b6</t>
         </is>
@@ -3224,17 +3500,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr">
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
         <is>
           <t>1ac36d3f-3503-4dbc-8663-90c00452f8f0</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr">
+      <c r="Q61" t="inlineStr">
         <is>
           <t>f94365bb-dcec-423a-a128-69b3dd5acbe8</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr">
+      <c r="R61" t="inlineStr">
         <is>
           <t>1b2534aa-8b82-4a86-ab3f-f25c4c4483a3</t>
         </is>
@@ -3278,25 +3559,30 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr">
+      <c r="O62" t="inlineStr">
         <is>
           <t>On a clean hit damage will be 43 and the opponent is knocked down.</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr">
+      <c r="P62" t="inlineStr">
         <is>
           <t>32805c14-f4cd-468e-bce2-3f99b661f511</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr">
+      <c r="Q62" t="inlineStr">
         <is>
           <t>f887b34b-5bf7-4ba1-8429-5f9cced91971</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr">
+      <c r="R62" t="inlineStr">
         <is>
           <t>1ac36d3f-3503-4dbc-8663-90c00452f8f0</t>
         </is>
@@ -3335,20 +3621,25 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr">
+      <c r="P63" t="inlineStr">
         <is>
           <t>ec808cdb-142e-457c-9e63-ee7cb1ab1e08</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr">
+      <c r="Q63" t="inlineStr">
         <is>
           <t>9646c1c3-2ab3-4203-a85c-870c0905b64b</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr">
+      <c r="R63" t="inlineStr">
         <is>
           <t>32805c14-f4cd-468e-bce2-3f99b661f511</t>
         </is>
@@ -3387,20 +3678,25 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
           <t>L</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr">
+      <c r="P64" t="inlineStr">
         <is>
           <t>db554e15-9dd5-40bb-a681-78c2cb6b50bc</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr">
+      <c r="Q64" t="inlineStr">
         <is>
           <t>d75d590a-9e2b-4b0e-841d-694baca41bfe</t>
         </is>
       </c>
-      <c r="Q64" t="inlineStr">
+      <c r="R64" t="inlineStr">
         <is>
           <t>32805c14-f4cd-468e-bce2-3f99b661f511</t>
         </is>
@@ -3444,30 +3740,35 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
           <t>h</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
+      <c r="N65" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr">
+      <c r="O65" t="inlineStr">
         <is>
           <t>When no tag is buffered on a counterhit you cannot juggle.; When a Tag is buffered (~5) all Wind Godfists hit Special Mid. Electric Wind Godfist causes GB.</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr">
+      <c r="P65" t="inlineStr">
         <is>
           <t>21a7ca65-38cc-4c3c-9201-26510decb0b1</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr">
+      <c r="Q65" t="inlineStr">
         <is>
           <t>808ca106-be9c-4427-b53b-ad72b7191a45</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr">
+      <c r="R65" t="inlineStr">
         <is>
           <t>1ac36d3f-3503-4dbc-8663-90c00452f8f0</t>
         </is>
@@ -3511,30 +3812,35 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
           <t>L</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr">
+      <c r="N66" t="inlineStr">
         <is>
           <t>JG BS</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr">
+      <c r="O66" t="inlineStr">
         <is>
           <t>Delayed Hell Sweep will do 15 damage.</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr">
+      <c r="P66" t="inlineStr">
         <is>
           <t>924c9b14-97be-4ca5-ba8f-9bba0c6b200c</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr">
+      <c r="Q66" t="inlineStr">
         <is>
           <t>e19b04f7-fa46-45c6-ad45-082db6cd6f72</t>
         </is>
       </c>
-      <c r="Q66" t="inlineStr">
+      <c r="R66" t="inlineStr">
         <is>
           <t>1ac36d3f-3503-4dbc-8663-90c00452f8f0</t>
         </is>
@@ -3573,20 +3879,25 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr">
+      <c r="P67" t="inlineStr">
         <is>
           <t>19f58a55-6e04-4800-92e8-2a9f9634e1b3</t>
         </is>
       </c>
-      <c r="P67" t="inlineStr">
+      <c r="Q67" t="inlineStr">
         <is>
           <t>304ed77b-d5e6-4f96-8310-28f837a8a331</t>
         </is>
       </c>
-      <c r="Q67" t="inlineStr">
+      <c r="R67" t="inlineStr">
         <is>
           <t>924c9b14-97be-4ca5-ba8f-9bba0c6b200c</t>
         </is>
@@ -3630,20 +3941,25 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
           <t>hhm</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr">
+      <c r="N68" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="O68" t="inlineStr">
+      <c r="P68" t="inlineStr">
         <is>
           <t>aa1f7bcf-d6c5-4a66-92db-b709d925fed9</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr">
+      <c r="Q68" t="inlineStr">
         <is>
           <t>66647df7-5707-4ccd-a047-75919930e4fd</t>
         </is>
@@ -3682,20 +3998,25 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O69" t="inlineStr">
+      <c r="P69" t="inlineStr">
         <is>
           <t>be6db272-1872-48d5-9c9c-0d0d059d5ada</t>
         </is>
       </c>
-      <c r="P69" t="inlineStr">
+      <c r="Q69" t="inlineStr">
         <is>
           <t>e899180b-907f-47fe-b4c1-51f3ed45d0ca</t>
         </is>
       </c>
-      <c r="Q69" t="inlineStr">
+      <c r="R69" t="inlineStr">
         <is>
           <t>aa1f7bcf-d6c5-4a66-92db-b709d925fed9</t>
         </is>
@@ -3734,20 +4055,25 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O70" t="inlineStr">
+      <c r="P70" t="inlineStr">
         <is>
           <t>b8dda983-35af-47e1-81b8-7d28611a9ca4</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr">
+      <c r="Q70" t="inlineStr">
         <is>
           <t>0b62fbc4-6648-4c9b-9255-56bc93cd8050</t>
         </is>
       </c>
-      <c r="Q70" t="inlineStr">
+      <c r="R70" t="inlineStr">
         <is>
           <t>aa1f7bcf-d6c5-4a66-92db-b709d925fed9</t>
         </is>
@@ -3791,15 +4117,20 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
           <t>shh</t>
         </is>
       </c>
-      <c r="O71" t="inlineStr">
+      <c r="P71" t="inlineStr">
         <is>
           <t>7727ab03-4896-4e56-a0cc-ef259d5609a1</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr">
+      <c r="Q71" t="inlineStr">
         <is>
           <t>ceb1087f-ef43-4ee6-9c5f-ca58d0717282</t>
         </is>
@@ -3838,20 +4169,25 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O72" t="inlineStr">
+      <c r="P72" t="inlineStr">
         <is>
           <t>4f2d088d-12f5-4b05-ba54-bb7c40204ad8</t>
         </is>
       </c>
-      <c r="P72" t="inlineStr">
+      <c r="Q72" t="inlineStr">
         <is>
           <t>9cf0dfcc-e927-4113-85ac-5bb883586652</t>
         </is>
       </c>
-      <c r="Q72" t="inlineStr">
+      <c r="R72" t="inlineStr">
         <is>
           <t>7727ab03-4896-4e56-a0cc-ef259d5609a1</t>
         </is>
@@ -3890,25 +4226,30 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
           <t>L</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr">
+      <c r="N73" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="O73" t="inlineStr">
+      <c r="P73" t="inlineStr">
         <is>
           <t>16c7aa83-e339-43c8-a2f8-aa7ab167725f</t>
         </is>
       </c>
-      <c r="P73" t="inlineStr">
+      <c r="Q73" t="inlineStr">
         <is>
           <t>31c4aaa9-a4ab-4af5-8d94-4e189b09df6e</t>
         </is>
       </c>
-      <c r="Q73" t="inlineStr">
+      <c r="R73" t="inlineStr">
         <is>
           <t>7727ab03-4896-4e56-a0cc-ef259d5609a1</t>
         </is>
@@ -3952,20 +4293,25 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr">
+      <c r="N74" t="inlineStr">
         <is>
           <t>JGc</t>
         </is>
       </c>
-      <c r="O74" t="inlineStr">
+      <c r="P74" t="inlineStr">
         <is>
           <t>9e1f3903-15f1-4a2c-a2a8-d83b2d52b8b1</t>
         </is>
       </c>
-      <c r="P74" t="inlineStr">
+      <c r="Q74" t="inlineStr">
         <is>
           <t>eee6d2a5-65ff-4b6d-ab74-72e968413ef6</t>
         </is>
@@ -4009,15 +4355,20 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
           <t>hh</t>
         </is>
       </c>
-      <c r="O75" t="inlineStr">
+      <c r="P75" t="inlineStr">
         <is>
           <t>a52b1077-3f2d-44b5-8bfd-7abb752d6c16</t>
         </is>
       </c>
-      <c r="P75" t="inlineStr">
+      <c r="Q75" t="inlineStr">
         <is>
           <t>f8fb3ca9-b75e-453e-b832-e17fa6dc20fa</t>
         </is>
@@ -4061,15 +4412,20 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
           <t>h</t>
         </is>
       </c>
-      <c r="O76" t="inlineStr">
+      <c r="P76" t="inlineStr">
         <is>
           <t>313d53a0-01cb-491d-ba60-b1ba2ab0d0db</t>
         </is>
       </c>
-      <c r="P76" t="inlineStr">
+      <c r="Q76" t="inlineStr">
         <is>
           <t>7db7cd03-9175-41af-beff-21dbec65f76d</t>
         </is>
@@ -4113,20 +4469,25 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
           <t>hh</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr">
+      <c r="N77" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="O77" t="inlineStr">
+      <c r="P77" t="inlineStr">
         <is>
           <t>e69bbfdd-c4a0-4d54-ac12-9a59e92ea818</t>
         </is>
       </c>
-      <c r="P77" t="inlineStr">
+      <c r="Q77" t="inlineStr">
         <is>
           <t>b1da4954-3ba2-4089-8137-ba663ba7033d</t>
         </is>
@@ -4170,20 +4531,25 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr">
+      <c r="N78" t="inlineStr">
         <is>
           <t>GB KS</t>
         </is>
       </c>
-      <c r="O78" t="inlineStr">
+      <c r="P78" t="inlineStr">
         <is>
           <t>fdc31ca3-48a9-4efa-8ccb-d201525fa498</t>
         </is>
       </c>
-      <c r="P78" t="inlineStr">
+      <c r="Q78" t="inlineStr">
         <is>
           <t>9ec0bb5c-013b-4ea4-94e6-2fd536123703</t>
         </is>
@@ -4222,20 +4588,25 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O79" t="inlineStr">
+      <c r="P79" t="inlineStr">
         <is>
           <t>f0a61edd-4f44-4b68-816e-20604e9decfe</t>
         </is>
       </c>
-      <c r="P79" t="inlineStr">
+      <c r="Q79" t="inlineStr">
         <is>
           <t>3726ac53-edb0-49f1-8d18-aeea5b883c73</t>
         </is>
       </c>
-      <c r="Q79" t="inlineStr">
+      <c r="R79" t="inlineStr">
         <is>
           <t>fdc31ca3-48a9-4efa-8ccb-d201525fa498</t>
         </is>
@@ -4244,7 +4615,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>WS 2 - [~5]</t>
+          <t>WS+2 - [~5]</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4279,15 +4650,20 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O80" t="inlineStr">
+      <c r="P80" t="inlineStr">
         <is>
           <t>b5c3b733-3b05-4b65-8aa7-137cfd48bec5</t>
         </is>
       </c>
-      <c r="P80" t="inlineStr">
+      <c r="Q80" t="inlineStr">
         <is>
           <t>9f12c745-f5fc-4502-9b1d-ed6949b920ec</t>
         </is>
@@ -4331,15 +4707,20 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O81" t="inlineStr">
+      <c r="P81" t="inlineStr">
         <is>
           <t>65a0ea49-07a7-499f-9581-0c1333c51a47</t>
         </is>
       </c>
-      <c r="P81" t="inlineStr">
+      <c r="Q81" t="inlineStr">
         <is>
           <t>c69d843f-ccc5-451c-9327-bd6d7462dee6</t>
         </is>
@@ -4348,7 +4729,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SS 2 - [~5]</t>
+          <t>SS+2 - [~5]</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4383,20 +4764,25 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr">
+      <c r="N82" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="O82" t="inlineStr">
+      <c r="P82" t="inlineStr">
         <is>
           <t>c6e4830e-a3cb-460d-9b03-0c4fe13b1861</t>
         </is>
       </c>
-      <c r="P82" t="inlineStr">
+      <c r="Q82" t="inlineStr">
         <is>
           <t>d9fd1d99-6c7f-4cee-b7c4-8e43b8eadb3c</t>
         </is>
@@ -4440,25 +4826,30 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
           <t>h</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr">
+      <c r="N83" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="N83" t="inlineStr">
+      <c r="O83" t="inlineStr">
         <is>
           <t>When no tag is buffered on a counterhit you cannot juggle.; When a Tag is buffered (~5) all Wind Godfists hit Special Mid. Electric Wind Godfist causes GB.</t>
         </is>
       </c>
-      <c r="O83" t="inlineStr">
+      <c r="P83" t="inlineStr">
         <is>
           <t>770ef824-eb8e-49ff-828c-c73385a322d8</t>
         </is>
       </c>
-      <c r="P83" t="inlineStr">
+      <c r="Q83" t="inlineStr">
         <is>
           <t>aa597aea-56c0-4bb7-bbef-181b56d3f130</t>
         </is>
@@ -4502,20 +4893,25 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
           <t>h</t>
         </is>
       </c>
-      <c r="M84" t="inlineStr">
+      <c r="N84" t="inlineStr">
         <is>
           <t>SH</t>
         </is>
       </c>
-      <c r="O84" t="inlineStr">
+      <c r="P84" t="inlineStr">
         <is>
           <t>f74f0a65-e789-461e-8435-0b5e83600664</t>
         </is>
       </c>
-      <c r="P84" t="inlineStr">
+      <c r="Q84" t="inlineStr">
         <is>
           <t>7825cdfc-53e7-41bd-b8a6-a855b81fa910</t>
         </is>
@@ -4559,25 +4955,30 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
           <t>h</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr">
+      <c r="N85" t="inlineStr">
         <is>
           <t>JG JGc</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr">
+      <c r="O85" t="inlineStr">
         <is>
           <t>When a Tag is buffered (~5) all Wind Godfists hit Special Mid. Electric Wind Godfist causes GB.</t>
         </is>
       </c>
-      <c r="O85" t="inlineStr">
+      <c r="P85" t="inlineStr">
         <is>
           <t>ae1401a6-1714-44f2-8821-a0baa135dd79</t>
         </is>
       </c>
-      <c r="P85" t="inlineStr">
+      <c r="Q85" t="inlineStr">
         <is>
           <t>be1a74c2-8f87-4609-afa7-dc9184b38436</t>
         </is>
@@ -4601,20 +5002,25 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="M86" t="inlineStr">
+      <c r="N86" t="inlineStr">
         <is>
           <t>DSc</t>
         </is>
       </c>
-      <c r="O86" t="inlineStr">
+      <c r="P86" t="inlineStr">
         <is>
           <t>fbf6020b-c701-4c61-a21a-2a9cf91994c2</t>
         </is>
       </c>
-      <c r="P86" t="inlineStr">
+      <c r="Q86" t="inlineStr">
         <is>
           <t>fcfe6800-c051-4c60-8ebb-1dba925779f6</t>
         </is>
@@ -4658,25 +5064,30 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
           <t>mmm</t>
         </is>
       </c>
-      <c r="M87" t="inlineStr">
+      <c r="N87" t="inlineStr">
         <is>
           <t>FSc</t>
         </is>
       </c>
-      <c r="N87" t="inlineStr">
+      <c r="O87" t="inlineStr">
         <is>
           <t>The stun occurs on the 2nd hit.</t>
         </is>
       </c>
-      <c r="O87" t="inlineStr">
+      <c r="P87" t="inlineStr">
         <is>
           <t>df4c3b3f-35a0-418c-935b-6a3cc714e622</t>
         </is>
       </c>
-      <c r="P87" t="inlineStr">
+      <c r="Q87" t="inlineStr">
         <is>
           <t>9fecf366-a307-49eb-b28d-41f90024c192</t>
         </is>
@@ -4720,25 +5131,30 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
           <t>mmm</t>
         </is>
       </c>
-      <c r="M88" t="inlineStr">
+      <c r="N88" t="inlineStr">
         <is>
           <t>JG FSc</t>
         </is>
       </c>
-      <c r="N88" t="inlineStr">
+      <c r="O88" t="inlineStr">
         <is>
           <t>The stun occurs on the 2nd hit.</t>
         </is>
       </c>
-      <c r="O88" t="inlineStr">
+      <c r="P88" t="inlineStr">
         <is>
           <t>99c069f9-a4c3-4982-9d97-b5409dcd7cdd</t>
         </is>
       </c>
-      <c r="P88" t="inlineStr">
+      <c r="Q88" t="inlineStr">
         <is>
           <t>d9765e4f-d363-4d86-86d8-c6c9b1d7a870</t>
         </is>
@@ -4782,20 +5198,25 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="M89" t="inlineStr">
+      <c r="N89" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="O89" t="inlineStr">
+      <c r="P89" t="inlineStr">
         <is>
           <t>a8af5950-edb9-4682-8d72-18378d0708d5</t>
         </is>
       </c>
-      <c r="P89" t="inlineStr">
+      <c r="Q89" t="inlineStr">
         <is>
           <t>ee7f03ae-efff-42b0-a39b-b15f044b9a86</t>
         </is>
@@ -4839,15 +5260,20 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
           <t>h</t>
         </is>
       </c>
-      <c r="O90" t="inlineStr">
+      <c r="P90" t="inlineStr">
         <is>
           <t>a39c346e-9b6b-4131-8daa-b88b7fd25259</t>
         </is>
       </c>
-      <c r="P90" t="inlineStr">
+      <c r="Q90" t="inlineStr">
         <is>
           <t>45d143f4-13b8-4eba-b8d0-a1a9a7e5b353</t>
         </is>
@@ -4891,20 +5317,25 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="M91" t="inlineStr">
+      <c r="N91" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="O91" t="inlineStr">
+      <c r="P91" t="inlineStr">
         <is>
           <t>64585d4f-ce41-42ba-9698-a3f8a88bf1d2</t>
         </is>
       </c>
-      <c r="P91" t="inlineStr">
+      <c r="Q91" t="inlineStr">
         <is>
           <t>b4f6d915-9ca9-46fc-9157-4f0c997c79b8</t>
         </is>
@@ -4913,7 +5344,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>WR 3</t>
+          <t>WR+3</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4953,20 +5384,25 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="M92" t="inlineStr">
+      <c r="N92" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="O92" t="inlineStr">
+      <c r="P92" t="inlineStr">
         <is>
           <t>68cbc93a-0539-4f0e-81a6-3d4c45f0f829</t>
         </is>
       </c>
-      <c r="P92" t="inlineStr">
+      <c r="Q92" t="inlineStr">
         <is>
           <t>a5bafe53-552b-49fd-90d0-4e83535abad9</t>
         </is>
@@ -5010,20 +5446,25 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
           <t>sh</t>
         </is>
       </c>
-      <c r="M93" t="inlineStr">
+      <c r="N93" t="inlineStr">
         <is>
           <t>JG GB</t>
         </is>
       </c>
-      <c r="O93" t="inlineStr">
+      <c r="P93" t="inlineStr">
         <is>
           <t>d5bd8f24-b46e-46c4-b044-d58438dfe3be</t>
         </is>
       </c>
-      <c r="P93" t="inlineStr">
+      <c r="Q93" t="inlineStr">
         <is>
           <t>16787ad0-a22f-4167-85d5-d76c2ab1d016</t>
         </is>
@@ -5067,15 +5508,20 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O94" t="inlineStr">
+      <c r="P94" t="inlineStr">
         <is>
           <t>e3754cba-9f84-439e-8d30-ff9150d53ae3</t>
         </is>
       </c>
-      <c r="P94" t="inlineStr">
+      <c r="Q94" t="inlineStr">
         <is>
           <t>17fec100-5d47-4817-89b9-184f74f89113</t>
         </is>
@@ -5119,20 +5565,25 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
           <t>M</t>
         </is>
       </c>
-      <c r="M95" t="inlineStr">
+      <c r="N95" t="inlineStr">
         <is>
           <t>GB CSc</t>
         </is>
       </c>
-      <c r="O95" t="inlineStr">
+      <c r="P95" t="inlineStr">
         <is>
           <t>336298c6-0c3d-47f2-82a6-9d3a8b11ce2f</t>
         </is>
       </c>
-      <c r="P95" t="inlineStr">
+      <c r="Q95" t="inlineStr">
         <is>
           <t>2d11dbdb-6a2e-489b-8c19-610c7de983e7</t>
         </is>
@@ -5176,15 +5627,20 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="O96" t="inlineStr">
+      <c r="P96" t="inlineStr">
         <is>
           <t>ce76da72-2fd7-4d3c-a276-7a94b91944c4</t>
         </is>
       </c>
-      <c r="P96" t="inlineStr">
+      <c r="Q96" t="inlineStr">
         <is>
           <t>f5fccfb6-5c33-48df-b67a-104ac4f0d9d5</t>
         </is>
@@ -5228,15 +5684,20 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="O97" t="inlineStr">
+      <c r="P97" t="inlineStr">
         <is>
           <t>8db9280b-917a-46e5-aecf-fd7b683e33f0</t>
         </is>
       </c>
-      <c r="P97" t="inlineStr">
+      <c r="Q97" t="inlineStr">
         <is>
           <t>0cc341f1-ca25-4619-8c1d-896ddd3085d2</t>
         </is>
@@ -5245,7 +5706,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>WS 4,4</t>
+          <t>WS+4,4</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -5280,15 +5741,20 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="O98" t="inlineStr">
+      <c r="P98" t="inlineStr">
         <is>
           <t>98df75bc-7a72-4ee3-ba14-2f7d466cb661</t>
         </is>
       </c>
-      <c r="P98" t="inlineStr">
+      <c r="Q98" t="inlineStr">
         <is>
           <t>79bc66dd-9efd-4eb4-b666-918266263133</t>
         </is>
@@ -5332,25 +5798,30 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
           <t>L</t>
         </is>
       </c>
-      <c r="M99" t="inlineStr">
+      <c r="N99" t="inlineStr">
         <is>
           <t>JG BS</t>
         </is>
       </c>
-      <c r="N99" t="inlineStr">
+      <c r="O99" t="inlineStr">
         <is>
           <t>Delayed Hell Sweep will do 15 damage.</t>
         </is>
       </c>
-      <c r="O99" t="inlineStr">
+      <c r="P99" t="inlineStr">
         <is>
           <t>e9f6cff8-a95f-4d33-91f6-0ad21241001f</t>
         </is>
       </c>
-      <c r="P99" t="inlineStr">
+      <c r="Q99" t="inlineStr">
         <is>
           <t>a778e855-8b54-4252-8729-b450b91db2ec</t>
         </is>
@@ -5389,20 +5860,25 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O100" t="inlineStr">
+      <c r="P100" t="inlineStr">
         <is>
           <t>e02a3aad-2719-4b53-836a-cc355339921a</t>
         </is>
       </c>
-      <c r="P100" t="inlineStr">
+      <c r="Q100" t="inlineStr">
         <is>
           <t>6f33dead-8e18-42ea-b5e4-dbd066054ad2</t>
         </is>
       </c>
-      <c r="Q100" t="inlineStr">
+      <c r="R100" t="inlineStr">
         <is>
           <t>e9f6cff8-a95f-4d33-91f6-0ad21241001f</t>
         </is>
@@ -5446,20 +5922,25 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
           <t>hLLm</t>
         </is>
       </c>
-      <c r="M101" t="inlineStr">
+      <c r="N101" t="inlineStr">
         <is>
           <t>BS</t>
         </is>
       </c>
-      <c r="O101" t="inlineStr">
+      <c r="P101" t="inlineStr">
         <is>
           <t>c155f9cf-5c28-4c82-8db4-9ef29f80ef8e</t>
         </is>
       </c>
-      <c r="P101" t="inlineStr">
+      <c r="Q101" t="inlineStr">
         <is>
           <t>05d296f9-b06e-46a2-afc5-bf6c7ce9e184</t>
         </is>
@@ -5503,15 +5984,20 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O102" t="inlineStr">
+      <c r="P102" t="inlineStr">
         <is>
           <t>198d48e3-fb8e-4387-b90f-d12b4dbd87ad</t>
         </is>
       </c>
-      <c r="P102" t="inlineStr">
+      <c r="Q102" t="inlineStr">
         <is>
           <t>93cae035-e68a-4565-bb24-bf140795eb5f</t>
         </is>
@@ -5538,17 +6024,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N103" t="inlineStr">
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
         <is>
           <t>Repels all attacks.</t>
         </is>
       </c>
-      <c r="O103" t="inlineStr">
+      <c r="P103" t="inlineStr">
         <is>
           <t>8d2d7bbe-a352-4a55-a376-1a80e099ac3d</t>
         </is>
       </c>
-      <c r="P103" t="inlineStr">
+      <c r="Q103" t="inlineStr">
         <is>
           <t>ecf1eb8f-c712-4f7d-a0b4-df4bc94c264e</t>
         </is>
@@ -5577,15 +6068,20 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
+          <t>varies</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O104" t="inlineStr">
+      <c r="P104" t="inlineStr">
         <is>
           <t>accd5398-5cb2-461a-897c-7c36276e215c</t>
         </is>
       </c>
-      <c r="P104" t="inlineStr">
+      <c r="Q104" t="inlineStr">
         <is>
           <t>69d1950c-de10-4cd7-8ef5-c0608de1b2e9</t>
         </is>
@@ -5614,15 +6110,20 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
+          <t>243034</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
           <t>M</t>
         </is>
       </c>
-      <c r="O105" t="inlineStr">
+      <c r="P105" t="inlineStr">
         <is>
           <t>be9e9c82-db19-4656-b369-46a4f2a6b4fb</t>
         </is>
       </c>
-      <c r="P105" t="inlineStr">
+      <c r="Q105" t="inlineStr">
         <is>
           <t>8a139512-feec-457f-97a8-dfc723fa9538</t>
         </is>
@@ -5654,12 +6155,12 @@
       </c>
       <c r="D108" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="E108" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="F108" s="1" t="inlineStr">
@@ -5684,45 +6185,50 @@
       </c>
       <c r="J108" s="1" t="inlineStr">
         <is>
+          <t>Damage Sum</t>
+        </is>
+      </c>
+      <c r="K108" s="1" t="inlineStr">
+        <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="K108" s="1" t="inlineStr">
+      <c r="L108" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="L108" s="1" t="inlineStr">
+      <c r="M108" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="M108" s="1" t="inlineStr">
+      <c r="N108" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="N108" s="1" t="inlineStr">
+      <c r="O108" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="O108" s="1" t="inlineStr">
+      <c r="P108" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="P108" s="1" t="inlineStr">
+      <c r="Q108" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Q108" s="1" t="inlineStr">
+      <c r="R108" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="R108" s="1" t="inlineStr">
+      <c r="S108" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -5749,12 +6255,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O109" t="inlineStr">
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
         <is>
           <t>f465515c-92ff-4acc-94d8-8ab298d28cf7</t>
         </is>
       </c>
-      <c r="P109" t="inlineStr">
+      <c r="Q109" t="inlineStr">
         <is>
           <t>8a0820ab-b687-470f-be5d-e7b334af9191</t>
         </is>
@@ -5781,22 +6292,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N110" t="inlineStr">
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
         <is>
           <t>Execute the command during the Lightning Force animation. The Possession will be activated after the Lightning Force.</t>
         </is>
       </c>
-      <c r="O110" t="inlineStr">
+      <c r="P110" t="inlineStr">
         <is>
           <t>3acf8755-bc41-435d-886b-79abd35a7116</t>
         </is>
       </c>
-      <c r="P110" t="inlineStr">
+      <c r="Q110" t="inlineStr">
         <is>
           <t>ed31fefd-0c5e-4f07-baea-6f6e17e9adde</t>
         </is>
       </c>
-      <c r="Q110" t="inlineStr">
+      <c r="R110" t="inlineStr">
         <is>
           <t>f465515c-92ff-4acc-94d8-8ab298d28cf7</t>
         </is>
@@ -5823,22 +6339,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N111" t="inlineStr">
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
         <is>
           <t>A fast command input will cancel the Lightning Force and the Devil Jin Possession is immediately activated.</t>
         </is>
       </c>
-      <c r="O111" t="inlineStr">
+      <c r="P111" t="inlineStr">
         <is>
           <t>30111b05-70f9-4da6-a877-84b3d46e3d8d</t>
         </is>
       </c>
-      <c r="P111" t="inlineStr">
+      <c r="Q111" t="inlineStr">
         <is>
           <t>83ac34fc-bf9b-4860-8814-6f3e50c86102</t>
         </is>
       </c>
-      <c r="Q111" t="inlineStr">
+      <c r="R111" t="inlineStr">
         <is>
           <t>f465515c-92ff-4acc-94d8-8ab298d28cf7</t>
         </is>
@@ -5867,20 +6388,25 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
           <t>throw</t>
         </is>
       </c>
-      <c r="N112" t="inlineStr">
+      <c r="O112" t="inlineStr">
         <is>
           <t>This throw is not escapable. During this throw you can see the markings on Jin's forehead and the red glowing eyes.</t>
         </is>
       </c>
-      <c r="O112" t="inlineStr">
+      <c r="P112" t="inlineStr">
         <is>
           <t>01abc1d9-351e-4d94-8b33-9a9388b698f1</t>
         </is>
       </c>
-      <c r="P112" t="inlineStr">
+      <c r="Q112" t="inlineStr">
         <is>
           <t>09de3ccf-b4fc-49f9-8be1-db65112e51d6</t>
         </is>
@@ -5924,15 +6450,20 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
           <t>hh</t>
         </is>
       </c>
-      <c r="O113" t="inlineStr">
+      <c r="P113" t="inlineStr">
         <is>
           <t>8fdb0781-ecd5-4a94-93c1-cedc0da09707</t>
         </is>
       </c>
-      <c r="P113" t="inlineStr">
+      <c r="Q113" t="inlineStr">
         <is>
           <t>17ed1c1d-f298-48b7-b44e-95231ec3f47b</t>
         </is>
@@ -5976,20 +6507,25 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="N114" t="inlineStr">
+      <c r="O114" t="inlineStr">
         <is>
           <t>This is similar to Heihachi's Thunder Godfist, you can not do the Mid Kick or Heel Sweep extension.</t>
         </is>
       </c>
-      <c r="O114" t="inlineStr">
+      <c r="P114" t="inlineStr">
         <is>
           <t>1abc5d56-3bec-430b-9112-1326fb6f329b</t>
         </is>
       </c>
-      <c r="P114" t="inlineStr">
+      <c r="Q114" t="inlineStr">
         <is>
           <t>7e8f123d-a441-4cf5-8446-b97f0a84435b</t>
         </is>
@@ -6033,20 +6569,25 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
+          <t>28 (9 to Jin)</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="M115" t="inlineStr">
+      <c r="N115" t="inlineStr">
         <is>
           <t>JG CFS</t>
         </is>
       </c>
-      <c r="O115" t="inlineStr">
+      <c r="P115" t="inlineStr">
         <is>
           <t>f88b7f72-befb-458e-9f09-b171b3fa9aa1</t>
         </is>
       </c>
-      <c r="P115" t="inlineStr">
+      <c r="Q115" t="inlineStr">
         <is>
           <t>2a2cf24e-7a76-4b70-a7af-29c412b7a21e</t>
         </is>
@@ -6090,25 +6631,30 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
+          <t>21 (19 to Jin)</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="M116" t="inlineStr">
+      <c r="N116" t="inlineStr">
         <is>
           <t>JG GB</t>
         </is>
       </c>
-      <c r="N116" t="inlineStr">
+      <c r="O116" t="inlineStr">
         <is>
           <t>Causes an incredible 27 frames of Guard Break when blocked. And it hits MID! Kazuya and Jun take 13 of Guard Damage.</t>
         </is>
       </c>
-      <c r="O116" t="inlineStr">
+      <c r="P116" t="inlineStr">
         <is>
           <t>211f25e8-b8a6-4fa7-8ad9-d36535fc143d</t>
         </is>
       </c>
-      <c r="P116" t="inlineStr">
+      <c r="Q116" t="inlineStr">
         <is>
           <t>2d78f4ac-401c-480c-85c6-5cf9d4ff22af</t>
         </is>
@@ -6152,25 +6698,30 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
+          <t>15 (13 to Jin)</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
           <t>L</t>
         </is>
       </c>
-      <c r="M117" t="inlineStr">
+      <c r="N117" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="N117" t="inlineStr">
+      <c r="O117" t="inlineStr">
         <is>
           <t>Is always a clean hit and will never cause Trip Stun.</t>
         </is>
       </c>
-      <c r="O117" t="inlineStr">
+      <c r="P117" t="inlineStr">
         <is>
           <t>a2b1ec57-c5bc-4b27-9cda-3cf4afbd5920</t>
         </is>
       </c>
-      <c r="P117" t="inlineStr">
+      <c r="Q117" t="inlineStr">
         <is>
           <t>0bde4271-90d2-4c99-8c1b-7bd7cd6e8150</t>
         </is>
@@ -6209,25 +6760,30 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="M118" t="inlineStr">
+      <c r="N118" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="O118" t="inlineStr">
+      <c r="P118" t="inlineStr">
         <is>
           <t>a10a23da-aabc-4d35-9416-b7146853501d</t>
         </is>
       </c>
-      <c r="P118" t="inlineStr">
+      <c r="Q118" t="inlineStr">
         <is>
           <t>bc390f24-a61c-4688-9423-3af7413b794a</t>
         </is>
       </c>
-      <c r="Q118" t="inlineStr">
+      <c r="R118" t="inlineStr">
         <is>
           <t>a2b1ec57-c5bc-4b27-9cda-3cf4afbd5920</t>
         </is>
@@ -6266,20 +6822,25 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
+          <t>21 (3 to Jin)</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O119" t="inlineStr">
+      <c r="P119" t="inlineStr">
         <is>
           <t>decc2ad9-7173-4de0-8cb8-0d5e861ad0c4</t>
         </is>
       </c>
-      <c r="P119" t="inlineStr">
+      <c r="Q119" t="inlineStr">
         <is>
           <t>2a0aa474-599f-4395-a7ab-a8ae63ac3aa6</t>
         </is>
       </c>
-      <c r="Q119" t="inlineStr">
+      <c r="R119" t="inlineStr">
         <is>
           <t>a10a23da-aabc-4d35-9416-b7146853501d</t>
         </is>
@@ -6303,20 +6864,25 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
           <t>hhhhhmh</t>
         </is>
       </c>
-      <c r="N120" t="inlineStr">
+      <c r="O120" t="inlineStr">
         <is>
           <t>This string is a true combo, once the left jab hits the rest cannot be blocked.</t>
         </is>
       </c>
-      <c r="O120" t="inlineStr">
+      <c r="P120" t="inlineStr">
         <is>
           <t>1ebe9db0-91f3-40f9-8e40-fbbd137c1ba2</t>
         </is>
       </c>
-      <c r="P120" t="inlineStr">
+      <c r="Q120" t="inlineStr">
         <is>
           <t>89b1af4d-9854-4bd2-87d7-447a3c00b29b</t>
         </is>
@@ -6348,12 +6914,12 @@
       </c>
       <c r="D123" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="E123" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="F123" s="1" t="inlineStr">
@@ -6378,45 +6944,50 @@
       </c>
       <c r="J123" s="1" t="inlineStr">
         <is>
+          <t>Damage Sum</t>
+        </is>
+      </c>
+      <c r="K123" s="1" t="inlineStr">
+        <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="K123" s="1" t="inlineStr">
+      <c r="L123" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="L123" s="1" t="inlineStr">
+      <c r="M123" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="M123" s="1" t="inlineStr">
+      <c r="N123" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="N123" s="1" t="inlineStr">
+      <c r="O123" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="O123" s="1" t="inlineStr">
+      <c r="P123" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="P123" s="1" t="inlineStr">
+      <c r="Q123" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Q123" s="1" t="inlineStr">
+      <c r="R123" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="R123" s="1" t="inlineStr">
+      <c r="S123" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -6455,15 +7026,20 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
           <t>!</t>
         </is>
       </c>
-      <c r="O124" t="inlineStr">
+      <c r="P124" t="inlineStr">
         <is>
           <t>974230d5-9099-4004-8908-af433c5cb42d</t>
         </is>
       </c>
-      <c r="P124" t="inlineStr">
+      <c r="Q124" t="inlineStr">
         <is>
           <t>1b5877c7-f5e4-470b-a90d-1f13e70937e5</t>
         </is>
@@ -6502,15 +7078,20 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
           <t>!</t>
         </is>
       </c>
-      <c r="O125" t="inlineStr">
+      <c r="P125" t="inlineStr">
         <is>
           <t>1fbc13b4-d496-4d8f-9512-7cd2ef99b777</t>
         </is>
       </c>
-      <c r="P125" t="inlineStr">
+      <c r="Q125" t="inlineStr">
         <is>
           <t>5746804f-e3c7-472d-8513-1e5511c2e41c</t>
         </is>
@@ -6542,12 +7123,12 @@
       </c>
       <c r="D128" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="E128" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="F128" s="1" t="inlineStr">
@@ -6572,45 +7153,50 @@
       </c>
       <c r="J128" s="1" t="inlineStr">
         <is>
+          <t>Damage Sum</t>
+        </is>
+      </c>
+      <c r="K128" s="1" t="inlineStr">
+        <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="K128" s="1" t="inlineStr">
+      <c r="L128" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="L128" s="1" t="inlineStr">
+      <c r="M128" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="M128" s="1" t="inlineStr">
+      <c r="N128" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="N128" s="1" t="inlineStr">
+      <c r="O128" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="O128" s="1" t="inlineStr">
+      <c r="P128" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="P128" s="1" t="inlineStr">
+      <c r="Q128" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Q128" s="1" t="inlineStr">
+      <c r="R128" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="R128" s="1" t="inlineStr">
+      <c r="S128" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -6629,15 +7215,20 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
           <t>hhhLmmlhhmm</t>
         </is>
       </c>
-      <c r="P129" t="inlineStr">
+      <c r="Q129" t="inlineStr">
         <is>
           <t>e55b194e-268a-481a-a9dc-9ef72e09f8d5</t>
         </is>
       </c>
-      <c r="R129" t="inlineStr">
+      <c r="S129" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -6656,15 +7247,20 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
           <t>hhhLmmlhhmL</t>
         </is>
       </c>
-      <c r="P130" t="inlineStr">
+      <c r="Q130" t="inlineStr">
         <is>
           <t>cb475c41-e8b6-4ff9-bd8e-37a458e72cd2</t>
         </is>
       </c>
-      <c r="R130" t="inlineStr">
+      <c r="S130" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -6683,15 +7279,20 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
           <t>hhhLmmlhhlh</t>
         </is>
       </c>
-      <c r="P131" t="inlineStr">
+      <c r="Q131" t="inlineStr">
         <is>
           <t>d026b17f-948b-4d7e-aeb1-e5f6517e00b6</t>
         </is>
       </c>
-      <c r="R131" t="inlineStr">
+      <c r="S131" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -6710,15 +7311,20 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
           <t>hhhhmmL h m m</t>
         </is>
       </c>
-      <c r="P132" t="inlineStr">
+      <c r="Q132" t="inlineStr">
         <is>
           <t>fcba9322-2509-43aa-bc78-28a39ed93851</t>
         </is>
       </c>
-      <c r="R132" t="inlineStr">
+      <c r="S132" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -6737,15 +7343,20 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
           <t>hhhhmmLLm!</t>
         </is>
       </c>
-      <c r="P133" t="inlineStr">
+      <c r="Q133" t="inlineStr">
         <is>
           <t>9b2b685a-64cd-4fba-a32a-f187bd907299</t>
         </is>
       </c>
-      <c r="R133" t="inlineStr">
+      <c r="S133" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -6764,15 +7375,20 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
           <t>hhmhlhhmmm</t>
         </is>
       </c>
-      <c r="P134" t="inlineStr">
+      <c r="Q134" t="inlineStr">
         <is>
           <t>1ba3e693-7890-4ba8-a3db-6fcafa95de8f</t>
         </is>
       </c>
-      <c r="R134" t="inlineStr">
+      <c r="S134" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -6791,15 +7407,20 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
           <t>hhmmlmLm!</t>
         </is>
       </c>
-      <c r="P135" t="inlineStr">
+      <c r="Q135" t="inlineStr">
         <is>
           <t>9a7af233-c051-469d-af17-0a10b3e720da</t>
         </is>
       </c>
-      <c r="R135" t="inlineStr">
+      <c r="S135" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -6818,15 +7439,20 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
           <t>hhmhlhhmm</t>
         </is>
       </c>
-      <c r="P136" t="inlineStr">
+      <c r="Q136" t="inlineStr">
         <is>
           <t>3fcee715-1e4a-4a97-80c0-5fd0b0294be6</t>
         </is>
       </c>
-      <c r="R136" t="inlineStr">
+      <c r="S136" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -6845,15 +7471,20 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
           <t>hhmhlhhmL</t>
         </is>
       </c>
-      <c r="P137" t="inlineStr">
+      <c r="Q137" t="inlineStr">
         <is>
           <t>3966b0f8-bc0b-466d-83fd-f2a82202f8d9</t>
         </is>
       </c>
-      <c r="R137" t="inlineStr">
+      <c r="S137" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -6872,15 +7503,20 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
           <t>hhmmm</t>
         </is>
       </c>
-      <c r="P138" t="inlineStr">
+      <c r="Q138" t="inlineStr">
         <is>
           <t>73b74b43-c81d-45eb-972e-07cbd1c76456</t>
         </is>
       </c>
-      <c r="R138" t="inlineStr">
+      <c r="S138" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>

--- a/sources/jin_step5.xlsx
+++ b/sources/jin_step5.xlsx
@@ -821,6 +821,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>8a32a40c-eb99-4c3e-83d9-8fb9cb6f62c4</t>
+        </is>
+      </c>
       <c r="Q8" t="inlineStr">
         <is>
           <t>8a32a40c-eb99-4c3e-83d9-8fb9cb6f62c4</t>
@@ -858,6 +863,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>9b654aae-43b4-4ee3-835c-083e97efa144</t>
+        </is>
+      </c>
       <c r="Q9" t="inlineStr">
         <is>
           <t>9b654aae-43b4-4ee3-835c-083e97efa144</t>
@@ -900,6 +910,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>7cbf5cdd-f696-407b-bc8d-f553aec297ca</t>
+        </is>
+      </c>
       <c r="Q10" t="inlineStr">
         <is>
           <t>7cbf5cdd-f696-407b-bc8d-f553aec297ca</t>
@@ -942,6 +957,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>9c909692-e175-413c-bb3d-d48e4dbe578e</t>
+        </is>
+      </c>
       <c r="Q11" t="inlineStr">
         <is>
           <t>9c909692-e175-413c-bb3d-d48e4dbe578e</t>
@@ -984,6 +1004,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>767ed810-48c3-4120-acc7-99c5a2660fcb</t>
+        </is>
+      </c>
       <c r="Q12" t="inlineStr">
         <is>
           <t>767ed810-48c3-4120-acc7-99c5a2660fcb</t>
@@ -1026,6 +1051,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>cda82971-a307-467e-ad05-57768181324c</t>
+        </is>
+      </c>
       <c r="Q13" t="inlineStr">
         <is>
           <t>cda82971-a307-467e-ad05-57768181324c</t>
@@ -1078,6 +1108,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>823249d7-37de-46b1-879b-61503eaa94c3</t>
+        </is>
+      </c>
       <c r="Q14" t="inlineStr">
         <is>
           <t>823249d7-37de-46b1-879b-61503eaa94c3</t>
@@ -1125,6 +1160,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>25dd8959-e3d5-46b4-9df3-7e812375a7d4</t>
+        </is>
+      </c>
       <c r="Q15" t="inlineStr">
         <is>
           <t>25dd8959-e3d5-46b4-9df3-7e812375a7d4</t>
@@ -1170,6 +1210,11 @@
       <c r="M16" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>67cda8df-b3c2-4b5d-83b0-595685761a80</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -7223,6 +7268,11 @@
           <t>hhhLmmlhhmm</t>
         </is>
       </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>e55b194e-268a-481a-a9dc-9ef72e09f8d5</t>
+        </is>
+      </c>
       <c r="Q129" t="inlineStr">
         <is>
           <t>e55b194e-268a-481a-a9dc-9ef72e09f8d5</t>
@@ -7255,6 +7305,11 @@
           <t>hhhLmmlhhmL</t>
         </is>
       </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>cb475c41-e8b6-4ff9-bd8e-37a458e72cd2</t>
+        </is>
+      </c>
       <c r="Q130" t="inlineStr">
         <is>
           <t>cb475c41-e8b6-4ff9-bd8e-37a458e72cd2</t>
@@ -7287,6 +7342,11 @@
           <t>hhhLmmlhhlh</t>
         </is>
       </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>d026b17f-948b-4d7e-aeb1-e5f6517e00b6</t>
+        </is>
+      </c>
       <c r="Q131" t="inlineStr">
         <is>
           <t>d026b17f-948b-4d7e-aeb1-e5f6517e00b6</t>
@@ -7319,6 +7379,11 @@
           <t>hhhhmmL h m m</t>
         </is>
       </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>fcba9322-2509-43aa-bc78-28a39ed93851</t>
+        </is>
+      </c>
       <c r="Q132" t="inlineStr">
         <is>
           <t>fcba9322-2509-43aa-bc78-28a39ed93851</t>
@@ -7351,6 +7416,11 @@
           <t>hhhhmmLLm!</t>
         </is>
       </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>9b2b685a-64cd-4fba-a32a-f187bd907299</t>
+        </is>
+      </c>
       <c r="Q133" t="inlineStr">
         <is>
           <t>9b2b685a-64cd-4fba-a32a-f187bd907299</t>
@@ -7383,6 +7453,11 @@
           <t>hhmhlhhmmm</t>
         </is>
       </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>1ba3e693-7890-4ba8-a3db-6fcafa95de8f</t>
+        </is>
+      </c>
       <c r="Q134" t="inlineStr">
         <is>
           <t>1ba3e693-7890-4ba8-a3db-6fcafa95de8f</t>
@@ -7415,6 +7490,11 @@
           <t>hhmmlmLm!</t>
         </is>
       </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>9a7af233-c051-469d-af17-0a10b3e720da</t>
+        </is>
+      </c>
       <c r="Q135" t="inlineStr">
         <is>
           <t>9a7af233-c051-469d-af17-0a10b3e720da</t>
@@ -7447,6 +7527,11 @@
           <t>hhmhlhhmm</t>
         </is>
       </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>3fcee715-1e4a-4a97-80c0-5fd0b0294be6</t>
+        </is>
+      </c>
       <c r="Q136" t="inlineStr">
         <is>
           <t>3fcee715-1e4a-4a97-80c0-5fd0b0294be6</t>
@@ -7479,6 +7564,11 @@
           <t>hhmhlhhmL</t>
         </is>
       </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>3966b0f8-bc0b-466d-83fd-f2a82202f8d9</t>
+        </is>
+      </c>
       <c r="Q137" t="inlineStr">
         <is>
           <t>3966b0f8-bc0b-466d-83fd-f2a82202f8d9</t>
@@ -7509,6 +7599,11 @@
       <c r="K138" t="inlineStr">
         <is>
           <t>hhmmm</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>73b74b43-c81d-45eb-972e-07cbd1c76456</t>
         </is>
       </c>
       <c r="Q138" t="inlineStr">

--- a/sources/jin_step5.xlsx
+++ b/sources/jin_step5.xlsx
@@ -843,6 +843,11 @@
           <t>– 1,2,1,2,1</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1,2,1,1,2</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
           <t>– Ultimate Punches</t>
@@ -888,6 +893,11 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>– 2,1,2,1,2</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2,1,2,2,1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
